--- a/artfynd/A 19538-2026 artfynd.xlsx
+++ b/artfynd/A 19538-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103518168</v>
+        <v>103518558</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510946.7355551329</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6686742.883202881</v>
+        <v>6686744</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,7 +747,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +757,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,6 +781,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>103518168</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>510947</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6686743</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
